--- a/users.xlsx
+++ b/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,6 +513,28 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>2026-04-25 23:01:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>winstone</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>504aa67206a83ec5457c01d7abf122a7bd7dc4be4b58ede1339e45d25edf37df</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-04-26 08:11:07</t>
         </is>
       </c>
     </row>

--- a/users.xlsx
+++ b/users.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,19 +468,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-04-25 22:59:56</t>
+          <t>2026-04-26 22:05:50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>mrkbnj</t>
+          <t>renmar</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>015dec7f6fbb52a523dfd9958fa45eea36547359e3aa6ef791a51bf3b9b79dbb</t>
+          <t>03260e49bae6610d654ab2035c09be3a47086794db26503b668811fe84a9dfa3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -490,19 +490,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-04-25 23:00:31</t>
+          <t>2026-04-26 22:06:38</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>andeng</t>
+          <t>andrea</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c41963edff5e6ae9b5a07c6d4374112a1480d46ebb66337c846218aa5942fc4a</t>
+          <t>5f3d6952c5c5e22077fabf461de80f1ce475752fe75afcf5ca46bac438405619</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -512,29 +512,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-04-25 23:01:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>winstone</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>504aa67206a83ec5457c01d7abf122a7bd7dc4be4b58ede1339e45d25edf37df</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>user</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2026-04-26 08:11:07</t>
+          <t>2026-04-26 22:10:10</t>
         </is>
       </c>
     </row>
